--- a/Sindhi Muslim/Classes/10-2-2025/Govt High School sindhi jamaat society.xlsx
+++ b/Sindhi Muslim/Classes/10-2-2025/Govt High School sindhi jamaat society.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Classes\10-2-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1278BE51-8779-441B-A66D-FC244096CFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A3A5E8-635A-491C-A822-65321CCCE67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4661,10 +4661,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5587,23 +5587,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="5" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
     </row>
     <row r="2" spans="1:15" s="9" customFormat="1" ht="15.75">
       <c r="A2" s="6" t="s">
@@ -8158,7 +8158,7 @@
       <c r="C57" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D57" s="68">
+      <c r="D57" s="67">
         <v>61</v>
       </c>
       <c r="E57" s="12" t="s">

--- a/Sindhi Muslim/Classes/10-2-2025/Govt High School sindhi jamaat society.xlsx
+++ b/Sindhi Muslim/Classes/10-2-2025/Govt High School sindhi jamaat society.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Classes\10-2-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A3A5E8-635A-491C-A822-65321CCCE67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F392B1E9-77E3-4624-B433-F83F39039C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Sindhi Muslim/Classes/10-2-2025/Govt High School sindhi jamaat society.xlsx
+++ b/Sindhi Muslim/Classes/10-2-2025/Govt High School sindhi jamaat society.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Classes\10-2-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F392B1E9-77E3-4624-B433-F83F39039C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5745255F-CE2E-4C2E-AEE0-FE333440B87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4369,7 +4369,7 @@
       <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4377,14 +4377,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4392,7 +4392,7 @@
       <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
